--- a/data/reports/_xvalidate_dashboard.xlsx
+++ b/data/reports/_xvalidate_dashboard.xlsx
@@ -17,16 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="0%&quot; (10/13 ・昨100/5d100)&quot;"/>
-    <numFmt numFmtId="165" formatCode="+0&quot; 億 (昨-96/5d-110)&quot;;-0&quot; 億 (昨-96/5d-110)&quot;;0&quot; 億&quot;"/>
-    <numFmt numFmtId="166" formatCode="0&quot; 檔 +9億 &quot;&quot;(昨14/5d10)&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0%&quot; 市+138億 &quot;&quot;(昨23/5d20)&quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;📅 明日預測 ↕ 中性 &quot;0.0&quot;% 信心 — P/C Ratio 主推 — 3 檔焦點&quot;"/>
+    <numFmt numFmtId="164" formatCode="0%&quot; (10/13, 累積中)&quot;"/>
+    <numFmt numFmtId="165" formatCode="+0.00&quot; 億 (累積中)&quot;;-0.00&quot; 億 (累積中)&quot;;0&quot; 億&quot;"/>
+    <numFmt numFmtId="166" formatCode="0&quot; 檔 (淨買 +9 億, 累積中)&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%&quot; (市場 +138 億, 累積中)&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;📅 明日預測 ↑ 偏多 &quot;0.0&quot;% 信心 — 外資現貨 主推 — 3 檔焦點&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;[Color10]-0.00%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,19 +67,19 @@
     <font>
       <name val="Noto Sans TC"/>
       <i val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <i val="1"/>
       <color rgb="FF059669"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Noto Sans TC"/>
-      <i val="1"/>
-      <color rgb="FF7C3AED"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans TC"/>
       <b val="1"/>
-      <color rgb="FF888888"/>
+      <color rgb="FF666666"/>
       <sz val="10"/>
     </font>
     <font>
@@ -124,7 +124,13 @@
     <font>
       <name val="Noto Sans TC"/>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Noto Sans TC"/>
@@ -137,6 +143,12 @@
       <b val="1"/>
       <color rgb="FFC62828"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans TC"/>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="30">
@@ -193,8 +205,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE5E7EB"/>
-        <bgColor rgb="FFE5E7EB"/>
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -301,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -324,7 +336,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -374,10 +386,10 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -389,7 +401,7 @@
     <xf numFmtId="0" fontId="12" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -397,19 +409,26 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -421,14 +440,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="18" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -819,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N106"/>
+  <dimension ref="B2:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -848,14 +863,14 @@
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🎯 1 強共識 / Q5 ↕ 中性 58.7% / E 0 異常 / F 0 長期 / J 10 集中 / H 6 借券壓力</t>
+          <t>🎯 1 強共識 / Q5 ↑ 偏多 81.7% / E 10 異常 / F 5 長期 / J 10 集中 / H 2 借券壓力</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>💡 📌 一般共識 9988 (Q5 中性, 中性信號)  |  避開 — 明日恐處置 5 檔: 3189/6213/8021...  |  訊號: 中性但 hot 多 (16 個信號 — 留意)</t>
+          <t>💡 📌 一般共識 9988 (Q5 偏多但無 master 量爆 — alpha 未啟動)  |  避開 — 明日恐處置 3 檔: 3625/4304/4971  |  訊號: 強偏多 (Q5 81.7%, hot=27)</t>
         </is>
       </c>
     </row>
@@ -876,28 +891,28 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>⭐ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 78.9% [63.7–88.9% 95% CI] (n=38, mean +4.37%) | 30d 實戰: 11/17 = 64.7% vs baseline 45.1% = +33.9pp — 強 alpha (p&lt;0.001)</t>
+          <t>⚠️ Phase 3.2 真 alpha (三訊號): 共識 ∩ Q5 偏多 ∩ master 量爆 hit 37.0% [27.8–47.2% 95% CI] (n=92, mean -0.91%) | 30d 實戰: 3/11 = 27.3% vs baseline 41.3% = -4.3pp — 樣本不足</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>💰 跟單實際淨報酬 (扣 0.585% 成本): 淨 hit 28/38 = 74% | 平均 +3.79% | 中位 +2.49% | 累積 +144% — 淨利 alpha 確認</t>
+          <t>⚠️ 跟單實際淨報酬 (扣 0.585% 成本): 淨 hit 27/92 = 29% | 平均 -1.49% | 中位 -1.81% | 累積 -137% — alpha 被成本吃光</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>🔬 Phase 3.5 多日 alpha (觀察期 n=38): 5 日內擇高 86.8% / +12.78%  |  premium 擇高 92.9% / +15.99% (n=28)  |  premium 持有 3 天 92.9% / +12.16%  — 來源: quad_hit_log × stock_history t+1~t+5</t>
+          <t>🚀 Phase 3.5 多日 alpha (正式): 5 日內擇高 67.3% / +3.61%  |  premium 擇高 72.0% / +5.44% (n=25)  |  premium 持有 3 天 60.0% / +3.00%  — 來源: quad_hit_log × stock_history t+1~t+5</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>💤 今日無 quad 訊號 (Q5=中性, 無 master 量爆)</t>
+          <t>💤 今日 Q5 偏多但無 master 量爆 — quad 三訊號未齊聚 (一般共識可參考但無 alpha 加持)</t>
         </is>
       </c>
     </row>
@@ -911,14 +926,14 @@
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>📌 大牌分析師 歷史 alpha: 全 picks n=1461 hit_1d=48% / hit_3d=51%  |  新標 n=302 hit_3d=49% mean=+0.96%  |  連加 n=69 hit_5d=59% mean=+3.86%</t>
+          <t>📌 大牌分析師 歷史 alpha: 全 picks n=1879 hit_1d=44% / hit_3d=46%  |  新標 n=112 hit_3d=48% mean=-0.19%  |  連加 n=85 hit_5d=53% mean=+0.85%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>ⓘ 排序: 合計淨買金額 ↓  |  ⭐⭐ = premium quad (陳律師/竹科主力/陳族元, ≥77% hit)  |  ⭐ = 一般 quad (78.9%)  |  ⚠️ = 領頭獨佔 ≥50%  |  🔁 = 過去 7 天 quad 重複  |  📌 = 你關注的 master (大牌分析師) 參與</t>
+          <t>ⓘ 排序: 合計淨買金額 ↓  |  ⭐⭐ = premium quad (陳律師/竹科主力/陳族元)  |  ⭐ = 一般 quad (37.0% 實測 n=92)  |  ⚠️ = 領頭獨佔 ≥50%  |  🔁 = 過去 7 天 quad 重複  |  📌 = 你關注的 master (大牌分析師) 參與</t>
         </is>
       </c>
     </row>
@@ -1085,13 +1100,13 @@
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="26" t="n">
-        <v>58.7</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>✅ 過去 30 天 P/C 命中率: 偏多 18/28 (64%) | 偏空 0/0 (0%) | 整體 18/28 (64%)</t>
+          <t>✅ 過去 30 天 P/C 命中率: 偏多 11/15 (73%) | 偏空 0/0 (0%) | 整體 11/15 (73%)</t>
         </is>
       </c>
     </row>
@@ -1332,1489 +1347,1515 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>✅ 今日無異常行為 (追蹤範圍內)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>巨人傑</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>巨人傑 今日買進 8 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>迷你哥/松山哥 今日買進 6 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F36" s="39" t="inlineStr">
+        <is>
+          <t>6 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>大牌分析師</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>大牌分析師 今日買進 5 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>Master</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>股票代號</t>
-        </is>
-      </c>
-      <c r="D38" s="40" t="inlineStr">
-        <is>
-          <t>連續天數</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>累計買金額(萬)</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>說明</t>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 今日買進 5 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F38" s="39" t="inlineStr">
+        <is>
+          <t>5 檔</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>尚無連續囤貨紀錄 (追蹤範圍內)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="41" t="inlineStr">
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tradow</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tradow 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>強森</t>
+        </is>
+      </c>
+      <c r="D40" s="39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E40" s="39" t="inlineStr">
+        <is>
+          <t>強森 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F40" s="39" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>林滄海</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>林滄海 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>民哥</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr">
+        <is>
+          <t>民哥 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F42" s="39" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>陳律師</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>陳律師 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>🆕 新標的</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>陳族元</t>
+        </is>
+      </c>
+      <c r="D44" s="39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E44" s="39" t="inlineStr">
+        <is>
+          <t>陳族元 今日買進 4 檔新標的 (過去從沒買過)</t>
+        </is>
+      </c>
+      <c r="F44" s="39" t="inlineStr">
+        <is>
+          <t>4 檔</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>… 另 3 筆 anomaly (詳見當日 sheet)</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="n"/>
+      <c r="D45" s="41" t="n"/>
+      <c r="E45" s="41" t="n"/>
+      <c r="F45" s="41" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>▍ F. 跨日連續囤貨 Top 30 (按連續天數排序)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>股票代號</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>連續天數</t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>累計買金額(萬)</t>
+        </is>
+      </c>
+      <c r="F48" s="43" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="n">
+        <v>33</v>
+      </c>
+      <c r="E49" t="n">
+        <v>641345</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>陳族元 連續 33 天加碼 6274 (累計 641,345 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D50" s="45" t="n">
+        <v>33</v>
+      </c>
+      <c r="E50" s="39" t="n">
+        <v>211048</v>
+      </c>
+      <c r="F50" s="39" t="inlineStr">
+        <is>
+          <t>強森 連續 33 天加碼 6669 (累計 211,048 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>🔴 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E51" t="n">
+        <v>890146</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>張濬安(航海王) 連續 30 天加碼 3008 (累計 890,146 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>🔴 強森</t>
+        </is>
+      </c>
+      <c r="C52" s="39" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="E52" s="39" t="n">
+        <v>88401</v>
+      </c>
+      <c r="F52" s="39" t="inlineStr">
+        <is>
+          <t>強森 連續 26 天加碼 3481 (累計 88,401 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>🔴 陳族元</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="D53" s="44" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" t="n">
+        <v>833440</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>陳族元 連續 25 天加碼 2308 (累計 833,440 萬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="46" t="inlineStr">
         <is>
           <t>▍ J. Master × Top 3 個股 cross-table (今日)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="42" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="47" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="C42" s="42" t="inlineStr">
+      <c r="C56" s="47" t="inlineStr">
         <is>
           <t>今日總買(萬)</t>
         </is>
       </c>
-      <c r="D42" s="42" t="inlineStr">
+      <c r="D56" s="47" t="inlineStr">
         <is>
           <t>Top1 個股</t>
         </is>
       </c>
-      <c r="E42" s="42" t="inlineStr">
+      <c r="E56" s="47" t="inlineStr">
         <is>
           <t>Top1 金額</t>
         </is>
       </c>
-      <c r="F42" s="42" t="inlineStr">
+      <c r="F56" s="47" t="inlineStr">
         <is>
           <t>Top2 個股</t>
         </is>
       </c>
-      <c r="G42" s="42" t="inlineStr">
+      <c r="G56" s="47" t="inlineStr">
         <is>
           <t>Top2 金額</t>
         </is>
       </c>
-      <c r="H42" s="42" t="inlineStr">
+      <c r="H56" s="47" t="inlineStr">
         <is>
           <t>Top3 個股</t>
         </is>
       </c>
-      <c r="I42" s="42" t="inlineStr">
+      <c r="I56" s="47" t="inlineStr">
         <is>
           <t>Top3 金額</t>
         </is>
       </c>
-      <c r="J42" s="42" t="inlineStr">
+      <c r="J56" s="47" t="inlineStr">
         <is>
           <t>Top3 合計%</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="31" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="31" t="inlineStr">
         <is>
           <t>🔥 民哥</t>
         </is>
       </c>
-      <c r="C43" s="32" t="n">
+      <c r="C57" s="32" t="n">
         <v>59000</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E43" s="32" t="n">
+      <c r="E57" s="32" t="n">
         <v>40000</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G43" s="32" t="n">
+      <c r="G57" s="32" t="n">
         <v>10000</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>聯發科(2454)</t>
         </is>
       </c>
-      <c r="I43" s="32" t="n">
+      <c r="I57" s="32" t="n">
         <v>9000</v>
       </c>
-      <c r="J43" s="43" t="n">
+      <c r="J57" s="48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="35" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="35" t="inlineStr">
         <is>
           <t>🔥 林滄海</t>
         </is>
       </c>
-      <c r="C44" s="32" t="n">
+      <c r="C58" s="32" t="n">
         <v>25600</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="E44" s="32" t="n">
+      <c r="E58" s="32" t="n">
         <v>12500</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="G44" s="32" t="n">
+      <c r="G58" s="32" t="n">
         <v>10100</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>鴻海(2317)</t>
         </is>
       </c>
-      <c r="I44" s="32" t="n">
+      <c r="I58" s="32" t="n">
         <v>3000</v>
       </c>
-      <c r="J44" s="43" t="n">
+      <c r="J58" s="48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="37" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>🔥 迷你哥/松山哥</t>
         </is>
       </c>
-      <c r="C45" s="32" t="n">
+      <c r="C59" s="32" t="n">
         <v>15500</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E45" s="32" t="n">
+      <c r="E59" s="32" t="n">
         <v>10500</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>台積電(2330)</t>
         </is>
       </c>
-      <c r="G45" s="32" t="n">
+      <c r="G59" s="32" t="n">
         <v>5000</v>
       </c>
-      <c r="J45" s="43" t="n">
+      <c r="J59" s="48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="44" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="49" t="inlineStr">
         <is>
           <t>🔥 巨人傑</t>
         </is>
       </c>
-      <c r="C46" s="32" t="n">
+      <c r="C60" s="32" t="n">
         <v>10900</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E46" s="32" t="n">
+      <c r="E60" s="32" t="n">
         <v>10900</v>
       </c>
-      <c r="J46" s="43" t="n">
+      <c r="J60" s="48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="36" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="36" t="inlineStr">
         <is>
           <t>🔥 Tradow</t>
         </is>
       </c>
-      <c r="C47" s="32" t="n">
+      <c r="C61" s="32" t="n">
         <v>10800</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E47" s="32" t="n">
+      <c r="E61" s="32" t="n">
         <v>10800</v>
       </c>
-      <c r="J47" s="43" t="n">
+      <c r="J61" s="48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="45" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="50" t="inlineStr">
         <is>
           <t>🔥 強森</t>
         </is>
       </c>
-      <c r="C48" s="32" t="n">
+      <c r="C62" s="32" t="n">
         <v>10700</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>強共識股(9988)</t>
         </is>
       </c>
-      <c r="E48" s="32" t="n">
+      <c r="E62" s="32" t="n">
         <v>10700</v>
       </c>
-      <c r="J48" s="43" t="n">
+      <c r="J62" s="48" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="46" t="inlineStr">
-        <is>
-          <t>🔥 布哥/n_nchang</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="n">
-        <v>10600</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E49" s="32" t="n">
-        <v>10600</v>
-      </c>
-      <c r="J49" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="47" t="inlineStr">
-        <is>
-          <t>🔥 陳律師</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="n">
-        <v>10400</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E50" s="32" t="n">
-        <v>10400</v>
-      </c>
-      <c r="J50" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="48" t="inlineStr">
-        <is>
-          <t>🔥 陳族元</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="n">
-        <v>10300</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E51" s="32" t="n">
-        <v>10300</v>
-      </c>
-      <c r="J51" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="34" t="inlineStr">
-        <is>
-          <t>🔥 張濬安(航海王)</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="n">
-        <v>10200</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>強共識股(9988)</t>
-        </is>
-      </c>
-      <c r="E52" s="32" t="n">
-        <v>10200</v>
-      </c>
-      <c r="J52" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="B54" s="49" t="inlineStr">
-        <is>
-          <t>▍ G. 注意股 (資料日 20260701)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="50" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C55" s="50" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D55" s="50" t="inlineStr">
-        <is>
-          <t>累計次數</t>
-        </is>
-      </c>
-      <c r="E55" s="50" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F55" s="50" t="inlineStr">
-        <is>
-          <t>本益比</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>059570</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>強茂凱基5B購03</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="51" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="C57" s="51" t="inlineStr">
-        <is>
-          <t>中福</t>
-        </is>
-      </c>
-      <c r="D57" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="51" t="n">
-        <v>30.05</v>
-      </c>
-      <c r="F57" s="51" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="51" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="C59" s="51" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="D59" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="51" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="F59" s="51" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="51" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="C61" s="51" t="inlineStr">
-        <is>
-          <t>東聯</t>
-        </is>
-      </c>
-      <c r="D61" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="51" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F61" s="51" t="inlineStr">
-        <is>
-          <t>-----</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>51.67</t>
-        </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="C63" s="51" t="inlineStr">
-        <is>
-          <t>宏旭-KY</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="n">
+          <t>🔥 布哥/n_nchang</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>10600</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>10600</v>
+      </c>
+      <c r="J63" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="51" t="n">
-        <v>62</v>
-      </c>
-      <c r="F63" s="51" t="inlineStr">
-        <is>
-          <t>24.90</t>
-        </is>
-      </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
+      <c r="B64" s="52" t="inlineStr">
+        <is>
+          <t>🔥 陳律師</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>10400</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>10400</v>
+      </c>
+      <c r="J64" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="n">
-        <v>169</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>42.46</t>
-        </is>
-      </c>
     </row>
     <row r="65">
-      <c r="B65" s="51" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="C65" s="51" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="n">
+      <c r="B65" s="53" t="inlineStr">
+        <is>
+          <t>🔥 陳族元</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>10300</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>10300</v>
+      </c>
+      <c r="J65" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="51" t="n">
-        <v>2660</v>
-      </c>
-      <c r="F65" s="51" t="inlineStr">
-        <is>
-          <t>50.30</t>
-        </is>
-      </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2363</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
+      <c r="B66" s="34" t="inlineStr">
+        <is>
+          <t>🔥 張濬安(航海王)</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>10200</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>強共識股(9988)</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>10200</v>
+      </c>
+      <c r="J66" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>43.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="51" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="C67" s="51" t="inlineStr">
-        <is>
-          <t>凱美</t>
-        </is>
-      </c>
-      <c r="D67" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="51" t="n">
-        <v>232.5</v>
-      </c>
-      <c r="F67" s="51" t="inlineStr">
-        <is>
-          <t>70.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>國碩</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-----</t>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="54" t="inlineStr">
+        <is>
+          <t>▍ G. 注意股 (資料日 20260921)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="51" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="C69" s="51" t="inlineStr">
-        <is>
-          <t>希華</t>
-        </is>
-      </c>
-      <c r="D69" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="51" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="F69" s="51" t="inlineStr">
-        <is>
-          <t>107.84</t>
+      <c r="B69" s="55" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C69" s="55" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D69" s="55" t="inlineStr">
+        <is>
+          <t>累計次數</t>
+        </is>
+      </c>
+      <c r="E69" s="55" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="F69" s="55" t="inlineStr">
+        <is>
+          <t>本益比</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>333</v>
+        <v>27.05</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>26.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260701)</t>
+          <t>-----</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="39" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="C71" s="39" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+      <c r="D71" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="39" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F71" s="39" t="inlineStr">
+        <is>
+          <t>71.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>環科</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>54</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>14.40</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>借券張數</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>融券張數</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>ratio</t>
+      <c r="B73" s="39" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="D73" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="39" t="n">
+        <v>572</v>
+      </c>
+      <c r="F73" s="39" t="inlineStr">
+        <is>
+          <t>140.20</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="52" t="inlineStr">
-        <is>
-          <t>🔴 2887</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2468</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>13846</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" s="53" t="n">
-        <v>4615.33</v>
+          <t>華經</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>34.23</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C75" s="51" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D75" s="54" t="n">
-        <v>12974</v>
-      </c>
-      <c r="E75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="C75" s="39" t="inlineStr">
+        <is>
+          <t>瑞軒</t>
+        </is>
+      </c>
+      <c r="D75" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="39" t="n">
+        <v>43</v>
+      </c>
+      <c r="F75" s="39" t="inlineStr">
+        <is>
+          <t>30.94</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>11153</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>0</v>
+          <t>聯傑</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>56.8</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91.61</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="55" t="inlineStr">
-        <is>
-          <t>🔴 3231</t>
-        </is>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D77" s="54" t="n">
-        <v>11039</v>
-      </c>
-      <c r="E77" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" s="56" t="n">
-        <v>3679.67</v>
+      <c r="B77" s="39" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="C77" s="39" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="D77" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="39" t="n">
+        <v>952</v>
+      </c>
+      <c r="F77" s="39" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="52" t="inlineStr">
-        <is>
-          <t>🔴 2002</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3443</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>8477</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" s="53" t="n">
-        <v>1695.4</v>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7615</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>195.21</t>
+        </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="51" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C79" s="51" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D79" s="54" t="n">
-        <v>7892</v>
-      </c>
-      <c r="E79" s="54" t="n">
-        <v>451</v>
-      </c>
-      <c r="F79" s="57" t="n">
-        <v>17.5</v>
+      <c r="B79" s="39" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="C79" s="39" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="D79" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="39" t="n">
+        <v>545</v>
+      </c>
+      <c r="F79" s="39" t="inlineStr">
+        <is>
+          <t>110.55</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="n">
-        <v>7786</v>
-      </c>
-      <c r="E80" s="32" t="n">
-        <v>437</v>
-      </c>
-      <c r="F80" s="58" t="n">
-        <v>17.82</v>
+          <t>宏致</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>169</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>44.47</t>
+        </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="55" t="inlineStr">
-        <is>
-          <t>🔴 1101</t>
-        </is>
-      </c>
-      <c r="C81" s="51" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D81" s="54" t="n">
-        <v>7348</v>
-      </c>
-      <c r="E81" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F81" s="56" t="n">
-        <v>3674</v>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C81" s="39" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D81" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="39" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="F81" s="39" t="inlineStr">
+        <is>
+          <t>99.68</t>
+        </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="52" t="inlineStr">
-        <is>
-          <t>🔴 0056</t>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>6168</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>7238</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F82" s="53" t="n">
-        <v>1809.5</v>
+          <t>宏齊</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>133.44</t>
+        </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="51" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C83" s="51" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D83" s="54" t="n">
-        <v>6334</v>
-      </c>
-      <c r="E83" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
+        <is>
+          <t>光鼎</t>
+        </is>
+      </c>
+      <c r="D83" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="39" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F83" s="39" t="inlineStr">
+        <is>
+          <t>-----</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="52" t="inlineStr">
-        <is>
-          <t>🔴 2886</t>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6668</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D84" s="32" t="n">
-        <v>6035</v>
-      </c>
-      <c r="E84" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" s="53" t="n">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="51" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="C85" s="51" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="D85" s="54" t="n">
-        <v>5782</v>
-      </c>
-      <c r="E85" s="54" t="n">
-        <v>74</v>
-      </c>
-      <c r="F85" s="57" t="n">
-        <v>78.14</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D86" s="32" t="n">
-        <v>5366</v>
-      </c>
-      <c r="E86" s="32" t="n">
-        <v>278</v>
-      </c>
-      <c r="F86" s="58" t="n">
-        <v>19.3</v>
+          <t>中揚光</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-----</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>▍ H. 借券賣出 Top 15 (機構級反向力量, 資料日 20260921)</t>
+        </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="51" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C87" s="51" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D87" s="54" t="n">
-        <v>5179</v>
-      </c>
-      <c r="E87" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>借券張數</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>融券張數</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>瑞軒</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>5112</v>
+        <v>15293</v>
       </c>
       <c r="E88" s="32" t="n">
-        <v>602</v>
-      </c>
-      <c r="F88" s="58" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="B90" s="59" t="inlineStr">
-        <is>
-          <t>▍ I. 未來 30 天除權息 (有效 306 檔, 已剔除過期)</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="F88" s="56" t="n">
+        <v>294.1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="39" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="C89" s="39" t="inlineStr">
+        <is>
+          <t>主動復華未來50</t>
+        </is>
+      </c>
+      <c r="D89" s="57" t="n">
+        <v>11185</v>
+      </c>
+      <c r="E89" s="57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" s="58" t="n">
+        <v>466.04</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E90" s="32" t="n">
+        <v>342</v>
+      </c>
+      <c r="F90" s="56" t="n">
+        <v>30.97</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="50" t="inlineStr">
-        <is>
-          <t>除權息日</t>
-        </is>
-      </c>
-      <c r="C91" s="50" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="D91" s="50" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="E91" s="50" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="F91" s="50" t="inlineStr">
-        <is>
-          <t>現金股利</t>
-        </is>
+      <c r="B91" s="45" t="inlineStr">
+        <is>
+          <t>🔴 2002</t>
+        </is>
+      </c>
+      <c r="C91" s="39" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D91" s="57" t="n">
+        <v>9119</v>
+      </c>
+      <c r="E91" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="59" t="n">
+        <v>4559.5</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>0.8</v>
+          <t>主動統一升級50</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="n">
+        <v>6084</v>
+      </c>
+      <c r="E92" s="32" t="n">
+        <v>554</v>
+      </c>
+      <c r="F92" s="56" t="n">
+        <v>10.98</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C93" s="51" t="inlineStr">
-        <is>
-          <t>1101B</t>
-        </is>
-      </c>
-      <c r="D93" s="51" t="inlineStr">
-        <is>
-          <t>台泥乙特</t>
-        </is>
-      </c>
-      <c r="E93" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F93" s="51" t="n">
-        <v>2.02625</v>
+      <c r="B93" s="39" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C93" s="39" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D93" s="57" t="n">
+        <v>4058</v>
+      </c>
+      <c r="E93" s="57" t="n">
+        <v>73</v>
+      </c>
+      <c r="F93" s="58" t="n">
+        <v>55.59</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>00673R</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1470</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>大統新創</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>0.65</v>
+          <t>期元大S&amp;P原油反1</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="n">
+        <v>3741</v>
+      </c>
+      <c r="E94" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F94" s="56" t="n">
+        <v>196.89</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C95" s="51" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="D95" s="51" t="inlineStr">
-        <is>
-          <t>元禎</t>
-        </is>
-      </c>
-      <c r="E95" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F95" s="51" t="n">
-        <v>1.07</v>
+      <c r="B95" s="39" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C95" s="39" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D95" s="57" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E95" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="F95" s="58" t="n">
+        <v>220.33</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>麗正</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>0.35</v>
+          <t>興富發</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="n">
+        <v>2963</v>
+      </c>
+      <c r="E96" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C97" s="51" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
-      <c r="D97" s="51" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="E97" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F97" s="51" t="n">
-        <v>42</v>
+      <c r="B97" s="45" t="inlineStr">
+        <is>
+          <t>🔴 00982A</t>
+        </is>
+      </c>
+      <c r="C97" s="39" t="inlineStr">
+        <is>
+          <t>主動群益台灣強棒</t>
+        </is>
+      </c>
+      <c r="D97" s="57" t="n">
+        <v>2893</v>
+      </c>
+      <c r="E97" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="59" t="n">
+        <v>2893</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>4.25</v>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D98" s="32" t="n">
+        <v>2650</v>
+      </c>
+      <c r="E98" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="56" t="n">
+        <v>331.25</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C99" s="51" t="inlineStr">
-        <is>
-          <t>2881A</t>
-        </is>
-      </c>
-      <c r="D99" s="51" t="inlineStr">
-        <is>
-          <t>富邦特</t>
-        </is>
-      </c>
-      <c r="E99" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F99" s="51" t="n">
-        <v>2.74875</v>
+      <c r="B99" s="39" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C99" s="39" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D99" s="57" t="n">
+        <v>2404</v>
+      </c>
+      <c r="E99" s="57" t="n">
+        <v>185</v>
+      </c>
+      <c r="F99" s="58" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2881B</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>富邦金乙特</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>2.572356</v>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="D100" s="32" t="n">
+        <v>2317</v>
+      </c>
+      <c r="E100" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="F100" s="56" t="n">
+        <v>105.32</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C101" s="51" t="inlineStr">
-        <is>
-          <t>2881C</t>
-        </is>
-      </c>
-      <c r="D101" s="51" t="inlineStr">
-        <is>
-          <t>富邦金丙特</t>
-        </is>
-      </c>
-      <c r="E101" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F101" s="51" t="n">
-        <v>1.8</v>
+      <c r="B101" s="39" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C101" s="39" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D101" s="57" t="n">
+        <v>2171</v>
+      </c>
+      <c r="E101" s="57" t="n">
+        <v>102</v>
+      </c>
+      <c r="F101" s="58" t="n">
+        <v>21.28</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C103" s="51" t="inlineStr">
-        <is>
-          <t>2887E</t>
-        </is>
-      </c>
-      <c r="D103" s="51" t="inlineStr">
-        <is>
-          <t>台新新光戊特一</t>
-        </is>
-      </c>
-      <c r="E103" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F103" s="51" t="n">
-        <v>2.43625</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2887F</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>台新新光戊特二</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>1.933601</v>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="n">
+        <v>2076</v>
+      </c>
+      <c r="E102" s="32" t="n">
+        <v>131</v>
+      </c>
+      <c r="F102" s="56" t="n">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="B104" s="60" t="inlineStr">
+        <is>
+          <t>▍ I. 未來 30 天除權息 (有效 26 檔, 已剔除過期)</t>
+        </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="51" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="C105" s="51" t="inlineStr">
-        <is>
-          <t>2887G</t>
-        </is>
-      </c>
-      <c r="D105" s="51" t="inlineStr">
-        <is>
-          <t>台新新光庚特一</t>
-        </is>
-      </c>
-      <c r="E105" s="51" t="inlineStr">
-        <is>
-          <t>息</t>
-        </is>
-      </c>
-      <c r="F105" s="51" t="n">
-        <v>1.71</v>
+      <c r="B105" s="55" t="inlineStr">
+        <is>
+          <t>除權息日</t>
+        </is>
+      </c>
+      <c r="C105" s="55" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="D105" s="55" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="E105" s="55" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F105" s="55" t="inlineStr">
+        <is>
+          <t>現金股利</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2887H</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>台新新光庚特二</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -2823,40 +2864,382 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="39" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C107" s="39" t="inlineStr">
+        <is>
+          <t>00930</t>
+        </is>
+      </c>
+      <c r="D107" s="39" t="inlineStr">
+        <is>
+          <t>永豐ESG低碳高息</t>
+        </is>
+      </c>
+      <c r="E107" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F107" s="39" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>名軒</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="39" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C109" s="39" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="D109" s="39" t="inlineStr">
+        <is>
+          <t>潤隆</t>
+        </is>
+      </c>
+      <c r="E109" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F109" s="39" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>興富發</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="39" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C111" s="39" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="D111" s="39" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="E111" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F111" s="39" t="n">
+        <v>1.007326</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>興泰</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>權息</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="39" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D113" s="39" t="inlineStr">
+        <is>
+          <t>華豐</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F113" s="39" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>聚賢研發-創</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="39" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C115" s="39" t="inlineStr">
+        <is>
+          <t>01004T</t>
+        </is>
+      </c>
+      <c r="D115" s="39" t="inlineStr">
+        <is>
+          <t>土銀富邦R2</t>
+        </is>
+      </c>
+      <c r="E115" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F115" s="39" t="n">
+        <v>0.221074</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>中環</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="39" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="D117" s="39" t="inlineStr">
+        <is>
+          <t>泰銘</t>
+        </is>
+      </c>
+      <c r="E117" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F117" s="39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>6834</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>天二科技</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="39" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>00406A</t>
+        </is>
+      </c>
+      <c r="D119" s="39" t="inlineStr">
+        <is>
+          <t>主動中信台灣收益</t>
+        </is>
+      </c>
+      <c r="E119" s="39" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="F119" s="39" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>00939</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>統一台灣高息動能</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B37:J37"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B55:J55"/>
     <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B68:J68"/>
     <mergeCell ref="B33:J33"/>
     <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B86:J86"/>
     <mergeCell ref="B12:N12"/>
     <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B41:J41"/>
     <mergeCell ref="B21:N21"/>
     <mergeCell ref="B11:N11"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B54:J54"/>
-    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B47:J47"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="B90:J90"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B10:N10"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <conditionalFormatting sqref="N16">
     <cfRule type="dataBar" priority="1">
@@ -2894,8 +3277,26 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43:C52">
+  <conditionalFormatting sqref="D49:D53">
     <cfRule type="dataBar" priority="5">
+      <dataBar minLength="5" maxLength="90" showValue="1">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFEF5350"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49:E53">
+    <cfRule type="dataBar" priority="6">
+      <dataBar minLength="5" maxLength="90" showValue="1">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF81C784"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C57:C66">
+    <cfRule type="dataBar" priority="7">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2903,8 +3304,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J43:J52">
-    <cfRule type="dataBar" priority="6">
+  <conditionalFormatting sqref="J57:J66">
+    <cfRule type="dataBar" priority="8">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2912,8 +3313,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D56:D70">
-    <cfRule type="dataBar" priority="7">
+  <conditionalFormatting sqref="D70:D84">
+    <cfRule type="dataBar" priority="9">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2921,8 +3322,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D74:D88">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="D88:D102">
+    <cfRule type="dataBar" priority="10">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2930,8 +3331,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F74:F88">
-    <cfRule type="dataBar" priority="9">
+  <conditionalFormatting sqref="F88:F102">
+    <cfRule type="dataBar" priority="11">
       <dataBar minLength="5" maxLength="90" showValue="1">
         <cfvo type="min"/>
         <cfvo type="max"/>
